--- a/tools/precos/planilhas/precos-oficiais-celimax.xlsx
+++ b/tools/precos/planilhas/precos-oficiais-celimax.xlsx
@@ -41,7 +41,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -51,11 +51,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E3F4E8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF6DA"/>
       </patternFill>
     </fill>
     <fill>
@@ -77,7 +72,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -86,7 +81,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -643,9 +637,9 @@
       <c r="D3" s="2" t="n">
         <v>24.9</v>
       </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -700,7 +694,7 @@
       <c r="D4" s="2" t="n">
         <v>210.9</v>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>Conferir (tamanho/kit diferente)</t>
         </is>
@@ -757,7 +751,7 @@
       <c r="D5" s="2" t="n">
         <v>181.9</v>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>Conferir (tamanho/kit diferente)</t>
         </is>
@@ -814,7 +808,7 @@
       <c r="D6" s="2" t="n">
         <v>210.9</v>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Conferir (tamanho/kit diferente)</t>
         </is>
@@ -2929,7 +2923,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Site oficial: https://www.celimax.com · loja "CELIMAX NEW" · moeda USD · lido em 30/10/2026 06:02 UTC</t>
+          <t>Site oficial: https://www.celimax.com · loja "CELIMAX NEW" · moeda USD · lido em 30/10/2026 06:04 UTC</t>
         </is>
       </c>
     </row>

--- a/tools/precos/planilhas/precos-oficiais-celimax.xlsx
+++ b/tools/precos/planilhas/precos-oficiais-celimax.xlsx
@@ -41,7 +41,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -51,6 +51,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E3F4E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF6DA"/>
       </patternFill>
     </fill>
     <fill>
@@ -72,7 +77,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -81,6 +86,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -159,8 +165,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Comparacao" displayName="Comparacao" ref="A1:N6" headerRowCount="1">
-  <autoFilter ref="A1:N6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Comparacao" displayName="Comparacao" ref="A1:N55" headerRowCount="1">
+  <autoFilter ref="A1:N55"/>
   <tableColumns count="14">
     <tableColumn id="1" name="SKU"/>
     <tableColumn id="2" name="Nosso produto"/>
@@ -470,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -564,12 +570,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CX0022</t>
+          <t>CX0027</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Real Cica Niacinamide AC Calming Serum: sérum calmante de centella 40 ml</t>
+          <t>Derma Nature Relief Madecica pH Balancing Foam: espuma de limpeza com centella 150 ml</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -578,7 +584,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>189.9</v>
+        <v>101.9</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
@@ -587,16 +593,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>The Real Cica Niacinamide AC Calming Serum 40ml</t>
+          <t>Derma Nature Relief Madecica pH Balancing Foam Cleansing 150ml</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>40ml</t>
+          <t>150ml</t>
         </is>
       </c>
       <c r="H2" s="4" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="I2" s="4" t="n"/>
       <c r="J2" t="inlineStr">
@@ -606,7 +612,7 @@
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>https://www.celimax.com/products/celimax-the-real-cica-niacinamide-ac-calming-serum-40ml</t>
+          <t>https://www.celimax.com/products/celimax-derma-nature-relief-madecica-ph-balancing-foam-cleansing-150ml</t>
         </is>
       </c>
       <c r="L2" s="2">
@@ -621,12 +627,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CX0042-1</t>
+          <t>CX0020</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Real Noni Energy Ampoule Mask: máscara em folha com ampola de noni · 1 unidade</t>
+          <t>Dual Barrier Boosting Serum: sérum com 5 ceramidas e peptídeo 30 ml</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -635,7 +641,7 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>24.9</v>
+        <v>189.9</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
@@ -644,16 +650,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>The Real Noni Energy Ampoule Mask - 2 Size</t>
+          <t>Dual Barrier Boosting Serum 30ml</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1ea</t>
+          <t>30ml</t>
         </is>
       </c>
       <c r="H3" s="4" t="n">
-        <v>3.5</v>
+        <v>26</v>
       </c>
       <c r="I3" s="4" t="n"/>
       <c r="J3" t="inlineStr">
@@ -663,7 +669,7 @@
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>https://www.celimax.com/products/celimax-the-real-noni-energy-ampoule-mask-2-size?variant=67601377362229</t>
+          <t>https://www.celimax.com/products/celimax-dual-barrier-boosting-serum-30ml</t>
         </is>
       </c>
       <c r="L3" s="2">
@@ -678,12 +684,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CX0043-2</t>
+          <t>CX0004</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pore+Dark Spot Brightening Serum Mask: máscara em folha com niacinamida · Caixa com 10</t>
+          <t>Dual Barrier Creamy Toner: tônico cremoso com 5 ceramidas 150 ml</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -692,25 +698,25 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>210.9</v>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>Conferir (tamanho/kit diferente)</t>
+        <v>159.9</v>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pore+Dark Spot Brightening Serum Mask - 2 Size</t>
+          <t>Dual Barrier Creamy Toner 150ml</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1ea</t>
+          <t>150ml</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>3.5</v>
+        <v>24</v>
       </c>
       <c r="I4" s="4" t="n"/>
       <c r="J4" t="inlineStr">
@@ -720,7 +726,7 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>https://www.celimax.com/products/celimax-pore-dark-spot-brightening-serum-mask-2-size?variant=67601349935413</t>
+          <t>https://www.celimax.com/products/celimax-dual-barrier-creamy-toner-150ml</t>
         </is>
       </c>
       <c r="L4" s="2">
@@ -735,12 +741,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CX0017-1</t>
+          <t>CX0018</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TXA Body Clarifying Pad: discos esfoliantes para o corpo com ácido tranexâmico 50 un. · 1 pote (50 discos)</t>
+          <t>Dual Barrier Mild Gel Cleanser: gel de limpeza suave com ceramidas 200 ml</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -749,25 +755,25 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>181.9</v>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>Conferir (tamanho/kit diferente)</t>
+        <v>130.9</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ji Woo Gae One Step Body Brightening Pad 60pads</t>
+          <t>Dual Barrier Mild Gel Cleanser 200ml</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>60pad</t>
+          <t>200ml</t>
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I5" s="4" t="n"/>
       <c r="J5" t="inlineStr">
@@ -777,7 +783,7 @@
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>https://www.celimax.com/products/celimax-ji-woo-gae-one-step-body-brightening-pad-60pads</t>
+          <t>https://www.celimax.com/products/celimax-dual-barrier-mild-gel-cleanser-200ml</t>
         </is>
       </c>
       <c r="L5" s="2">
@@ -792,12 +798,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CX0039-2</t>
+          <t>CX0006</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Real Cica Calming Serum Mask: máscara em folha de centella com sérum · Caixa com 10</t>
+          <t>Dual Barrier Skin Wearable Cream: creme hidratante com 5 ceramidas 50 ml</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,21 +812,21 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>210.9</v>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Conferir (tamanho/kit diferente)</t>
+        <v>203.9</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>The Real Cica Calming Serum Mask - 2 Size</t>
+          <t>Dual Barrier Skin Wearable Cream 50ml</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>10ea</t>
+          <t>50ml</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
@@ -834,7 +840,7 @@
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>https://www.celimax.com/products/celimax-the-real-cica-calming-serum-mask-2-size?variant=67601249829173</t>
+          <t>https://www.celimax.com/products/celimax-dual-barrier-skin-wearable-cream-50ml</t>
         </is>
       </c>
       <c r="L6" s="2">
@@ -845,6 +851,2743 @@
         <f>IF(OR(D6="",L6=""),"",D6/L6-1)</f>
         <v/>
       </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CX0037</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dual Barrier Watery Sun Cream: protetor solar mineral FPS 50+ PA++++ 40 ml</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dual Barrier Watery Sun Cream 40ml</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>40ml</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-dual-barrier-watery-sun-cream-40ml</t>
+        </is>
+      </c>
+      <c r="L7" s="2">
+        <f>ROUND(H7*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M7" s="6">
+        <f>IF(OR(D7="",L7=""),"",D7/L7-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CX0030</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ji Woo Gae Baking Soda Deep Pore Foam Cleansing: espuma de limpeza dos poros 150 ml</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ji Woo Gae Baking Soda Deep Pore Foam Cleansing 150ml</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>150ml</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-ji-woo-gae-baking-soda-deep-pore-foam-cleansing-150ml</t>
+        </is>
+      </c>
+      <c r="L8" s="2">
+        <f>ROUND(H8*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M8" s="6">
+        <f>IF(OR(D8="",L8=""),"",D8/L8-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CX0019</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ji Woo Gae Cica BHA Blemish Toner Pad: discos com BHA, PHA e centella 60 unidades</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>145.9</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ji Woo Gae Cica BHA Blemish Toner Pad 60pad</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>60pad</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="I9" s="4" t="n"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-ji-woo-gae-cica-bha-blemish-toner-pad-60pad</t>
+        </is>
+      </c>
+      <c r="L9" s="2">
+        <f>ROUND(H9*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M9" s="6">
+        <f>IF(OR(D9="",L9=""),"",D9/L9-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CX0029</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ji Woo Gae Cica BHA Foam Cleansing: espuma de limpeza com centella e BHA 150 ml</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>115.9</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ji Woo Gae Cica BHA Acne Foam Cleansing 150ml</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>150ml</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="I10" s="4" t="n"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-ji-woo-gae-cica-bha-acne-foam-cleansing-150ml</t>
+        </is>
+      </c>
+      <c r="L10" s="2">
+        <f>ROUND(H10*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M10" s="6">
+        <f>IF(OR(D10="",L10=""),"",D10/L10-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CX0002</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ji Woo Gae Heartleaf BHA Peeling Pad: discos esfoliantes com BHA 60 unidades</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ji Woo Gae Heartleaf BHA Peeling Pad 60Pads</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>60pad</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-ji-woo-gae-heartleaf-bha-peeling-pad-60pads</t>
+        </is>
+      </c>
+      <c r="L11" s="2">
+        <f>ROUND(H11*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M11" s="6">
+        <f>IF(OR(D11="",L11=""),"",D11/L11-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CX0007</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ji Woo Gae One Step Body Brightening Pad: discos esfoliantes para o corpo 60 unidades</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ji Woo Gae One Step Body Brightening Pad 60pads</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>60pad</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-ji-woo-gae-one-step-body-brightening-pad-60pads</t>
+        </is>
+      </c>
+      <c r="L12" s="2">
+        <f>ROUND(H12*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M12" s="6">
+        <f>IF(OR(D12="",L12=""),"",D12/L12-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CX0025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ji Woo Gae One Step Mild Cleansing Pad: discos demaquilantes 60 unidades</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>174.9</v>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ji Woo Gae One Step Mild Cleansing Pad 60pads</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>60pad</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="I13" s="4" t="n"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-ji-woo-gae-one-step-mild-cleansing-pad-60pads</t>
+        </is>
+      </c>
+      <c r="L13" s="2">
+        <f>ROUND(H13*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M13" s="6">
+        <f>IF(OR(D13="",L13=""),"",D13/L13-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CX0024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Oil Control Moisturizing Cream: creme hidratante para pele oleosa 80 ml</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>145.9</v>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Oil Control Moisturizing Cream 80ml</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>80ml</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="I14" s="4" t="n"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-oil-control-moisturizing-cream-80ml</t>
+        </is>
+      </c>
+      <c r="L14" s="2">
+        <f>ROUND(H14*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M14" s="6">
+        <f>IF(OR(D14="",L14=""),"",D14/L14-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CX0031-1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Pore+Dark Spot Brightening Cream Mask: máscara de creme com niacinamida 20 g · 1 unidade</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Pore+Dark Spot Brightening Cream Mask - 2 Size</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1ea</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I15" s="4" t="n"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-pore-dark-spot-brightening-cream-mask-2-size?variant=67601354228021</t>
+        </is>
+      </c>
+      <c r="L15" s="2">
+        <f>ROUND(H15*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M15" s="6">
+        <f>IF(OR(D15="",L15=""),"",D15/L15-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CX0005-2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Pore+Dark Spot Brightening Pad: discos tônicos com niacinamida e ácido tranexâmico · 80 discos (175 ml)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>291.9</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Pore+Dark Spot Brightening Pad</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>40pad</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="I16" s="4" t="n"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-pore-dark-spot-brightening-pad-2-size?variant=67601349214517</t>
+        </is>
+      </c>
+      <c r="L16" s="2">
+        <f>ROUND(H16*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M16" s="6">
+        <f>IF(OR(D16="",L16=""),"",D16/L16-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CX0043-1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pore+Dark Spot Brightening Serum Mask: máscara em folha com niacinamida · 1 unidade</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Pore+Dark Spot Brightening Serum Mask - 2 Size</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1ea</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I17" s="4" t="n"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-pore-dark-spot-brightening-serum-mask-2-size?variant=67601349935413</t>
+        </is>
+      </c>
+      <c r="L17" s="2">
+        <f>ROUND(H17*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M17" s="6">
+        <f>IF(OR(D17="",L17=""),"",D17/L17-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CX0039-1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>The Real Cica Calming Serum Mask: máscara em folha de centella com sérum · 1 unidade</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>The Real Cica Calming Serum Mask - 2 Size</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1ea</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-the-real-cica-calming-serum-mask-2-size?variant=67601249861941</t>
+        </is>
+      </c>
+      <c r="L18" s="2">
+        <f>ROUND(H18*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M18" s="6">
+        <f>IF(OR(D18="",L18=""),"",D18/L18-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CX0022</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>The Real Cica Niacinamide AC Calming Serum: sérum calmante de centella 40 ml</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>189.9</v>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>The Real Cica Niacinamide AC Calming Serum 40ml</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>40ml</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-the-real-cica-niacinamide-ac-calming-serum-40ml</t>
+        </is>
+      </c>
+      <c r="L19" s="2">
+        <f>ROUND(H19*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M19" s="6">
+        <f>IF(OR(D19="",L19=""),"",D19/L19-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CX0014</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>The Real Cica Soothing Cream: gel-creme calmante de centella 50 ml</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>145.9</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>The Real Cica Soothing Cream 50ml</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>50ml</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="I20" s="4" t="n"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-the-real-cica-soothing-cream-50ml</t>
+        </is>
+      </c>
+      <c r="L20" s="2">
+        <f>ROUND(H20*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M20" s="6">
+        <f>IF(OR(D20="",L20=""),"",D20/L20-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CX0042-1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>The Real Noni Energy Ampoule Mask: máscara em folha com ampola de noni · 1 unidade</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>The Real Noni Energy Ampoule Mask - 2 Size</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1ea</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I21" s="4" t="n"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-the-real-noni-energy-ampoule-mask-2-size?variant=67601377362229</t>
+        </is>
+      </c>
+      <c r="L21" s="2">
+        <f>ROUND(H21*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M21" s="6">
+        <f>IF(OR(D21="",L21=""),"",D21/L21-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CX0012</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>The Real Noni Energy Repair Cream: creme calmante de noni com ceramida 50 ml</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>189.9</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>The Real Noni Energy Repair Cream 50ml</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>50ml</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="4" t="n"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-the-real-noni-energy-repair-cream-50ml-1</t>
+        </is>
+      </c>
+      <c r="L22" s="2">
+        <f>ROUND(H22*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M22" s="6">
+        <f>IF(OR(D22="",L22=""),"",D22/L22-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CX0021</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>The Real Noni Hydra Firming Lotion: loção hidratante leve de noni 150 ml</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>189.9</v>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>The Real Noni Hydra Firming Lotion 150ml</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>150ml</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="I23" s="4" t="n"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-the-real-noni-hydra-firming-lotion-150ml</t>
+        </is>
+      </c>
+      <c r="L23" s="2">
+        <f>ROUND(H23*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M23" s="6">
+        <f>IF(OR(D23="",L23=""),"",D23/L23-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CX0008</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>The Real Noni Moisture Balancing Toner: tônico hidratante de noni 150 ml</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>181.9</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>The Real Noni Moisture Balancing Toner 150ml</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>150ml</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="I24" s="4" t="n"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-the-real-noni-moisture-balancing-toner-150ml</t>
+        </is>
+      </c>
+      <c r="L24" s="2">
+        <f>ROUND(H24*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M24" s="6">
+        <f>IF(OR(D24="",L24=""),"",D24/L24-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CX0023</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>The Real Noni Refresh Clay Mask: máscara de argila com noni 120 g</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>115.9</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>The Real Noni Refresh Clay Mask 120g</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>120g</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="I25" s="4" t="n"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-the-real-noni-refresh-clay-mask-120g</t>
+        </is>
+      </c>
+      <c r="L25" s="2">
+        <f>ROUND(H25*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M25" s="6">
+        <f>IF(OR(D25="",L25=""),"",D25/L25-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CX0035</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Derma Nature Glutathione Longlasting Tone-up Cream: creme tone-up 35 ml</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Derma Nature Glutathione Longlasting Tone-up Cream 35ml</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>35ml</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="I26" s="4" t="n"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-derma-nature-glutathione-longlasting-tone-up-cream-35ml</t>
+        </is>
+      </c>
+      <c r="L26" s="2">
+        <f>ROUND(H26*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M26" s="6">
+        <f>IF(OR(D26="",L26=""),"",D26/L26-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CX0034</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Heart Pink Tone Up Sun Cream: protetor solar com cor rosada FPS 50+ PA++++ 40 ml</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>HEART PINK TONE UP SUN CREAM 40ml</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>40ml</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-heart-pink-tone-up-sun-cream-40ml</t>
+        </is>
+      </c>
+      <c r="L27" s="2">
+        <f>ROUND(H27*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M27" s="6">
+        <f>IF(OR(D27="",L27=""),"",D27/L27-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CX0040-1</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Ji Woo Gae Cica PHA Peel 2-Step Gel Mask: máscara em 2 passos com PHA e centella · 1 unidade</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ji Woo Gae Cica PHA Peel 2-Step Gel Mask - 2 Size</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1ea</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-ji-woo-gae-cica-pha-peel-2-step-gel-mask-2-size?variant=67601351180597</t>
+        </is>
+      </c>
+      <c r="L28" s="2">
+        <f>ROUND(H28*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M28" s="6">
+        <f>IF(OR(D28="",L28=""),"",D28/L28-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CX0044</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Oil Control Capsule Essence: essência matificante com cápsulas para pele oleosa 30 ml</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Oil Control Capsule Essence 30ml</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>30ml</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="I29" s="4" t="n"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-oil-control-capsule-essence-30ml</t>
+        </is>
+      </c>
+      <c r="L29" s="2">
+        <f>ROUND(H29*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M29" s="6">
+        <f>IF(OR(D29="",L29=""),"",D29/L29-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CX0041</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Oil Control Light Sunscreen: protetor solar matte FPS 50+ PA++++ 40 ml</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Oil Control Light Sunscreen 40ml</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>40ml</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="I30" s="4" t="n"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-oil-control-light-sunscreen-40ml</t>
+        </is>
+      </c>
+      <c r="L30" s="2">
+        <f>ROUND(H30*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M30" s="6">
+        <f>IF(OR(D30="",L30=""),"",D30/L30-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CX0036</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>The Real Noni Calming Glow Pad: discos calmantes de noni 50 unidades</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>174.9</v>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>The Real Noni Calming Glow Pad 50pads</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>50pads</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-the-real-noni-calming-glow-pad-50pads</t>
+        </is>
+      </c>
+      <c r="L31" s="2">
+        <f>ROUND(H31*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M31" s="6">
+        <f>IF(OR(D31="",L31=""),"",D31/L31-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CX0010</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Derma Nature Fresh Blackhead Jojoba Cleansing Oil: óleo de limpeza de jojoba 150 ml</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>130.9</v>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Derma Nature Fresh Blackhead Jojoba Cleansing Oil 150ml</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>150ml</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-derma-nature-fresh-blackhead-jojoba-cleansing-oil-150ml</t>
+        </is>
+      </c>
+      <c r="L32" s="2">
+        <f>ROUND(H32*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M32" s="6">
+        <f>IF(OR(D32="",L32=""),"",D32/L32-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>CX0016</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Dual Barrier Purifying Cleansing Balm: bálsamo de limpeza com ceramidas 50 ml</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>203.9</v>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Dual Barrier Purifying Cleansing Balm 50ml x 2ea</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>50ml x 2ea</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="I33" s="4" t="n"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-dual-barrier-purifying-cleansing-balm-50ml-x-2ea</t>
+        </is>
+      </c>
+      <c r="L33" s="2">
+        <f>ROUND(H33*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M33" s="6">
+        <f>IF(OR(D33="",L33=""),"",D33/L33-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>CX0009</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Pore+Dark Spot Brightening Cream: creme com ácido tranexâmico e niacinamida 35 ml</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>196.9</v>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Pore+Dark Spot Brightening Cream 35ml</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>35ml</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="I34" s="4" t="n"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-pore-dark-spot-brightening-cream-35ml</t>
+        </is>
+      </c>
+      <c r="L34" s="2">
+        <f>ROUND(H34*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M34" s="6">
+        <f>IF(OR(D34="",L34=""),"",D34/L34-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CX0005-1</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Pore+Dark Spot Brightening Pad: discos tônicos com niacinamida e ácido tranexâmico · 40 discos (100 ml)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Pore+Dark Spot Brightening Pad</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>40pad</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="I35" s="4" t="n"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-pore-dark-spot-brightening-pad-2-size?variant=67601349214517</t>
+        </is>
+      </c>
+      <c r="L35" s="2">
+        <f>ROUND(H35*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M35" s="6">
+        <f>IF(OR(D35="",L35=""),"",D35/L35-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>CX0011</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Pore+Dark Spot Brightening Serum: sérum com niacinamida e ácido tranexâmico 30 ml</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>196.9</v>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Pore+Dark Spot Brightening Serum 30ml</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>30ml</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="I36" s="4" t="n"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-pore-dark-spot-brightening-serum-30ml</t>
+        </is>
+      </c>
+      <c r="L36" s="2">
+        <f>ROUND(H36*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M36" s="6">
+        <f>IF(OR(D36="",L36=""),"",D36/L36-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CX0038-1</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>The Real Cica Calming Ampoule Mask: máscara em folha calmante de centella · 1 unidade</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>The Real Cica Calming Serum Mask - 2 Size</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1ea</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I37" s="4" t="n"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-the-real-cica-calming-serum-mask-2-size?variant=67601249861941</t>
+        </is>
+      </c>
+      <c r="L37" s="2">
+        <f>ROUND(H37*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M37" s="6">
+        <f>IF(OR(D37="",L37=""),"",D37/L37-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CX0003</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>The Real Noni Bubble Cleanser: espuma de limpeza com noni e BHA 155 ml</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>181.9</v>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>The Real Noni Acne Bubble Cleanser 155ml</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>155ml</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="I38" s="4" t="n"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-the-real-noni-acne-bubble-cleanser-155ml</t>
+        </is>
+      </c>
+      <c r="L38" s="2">
+        <f>ROUND(H38*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M38" s="6">
+        <f>IF(OR(D38="",L38=""),"",D38/L38-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CX0001-1</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>The Real Noni Energy Ampoule: sérum calmante e hidratante de noni · 30 ml</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>189.9</v>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>The Real Noni Energy Ampoule 30ml_MX</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>30ml</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="I39" s="4" t="n"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-the-real-noni-energy-ampoule-30ml_mx</t>
+        </is>
+      </c>
+      <c r="L39" s="2">
+        <f>ROUND(H39*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M39" s="6">
+        <f>IF(OR(D39="",L39=""),"",D39/L39-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>CX0001-2</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>The Real Noni Energy Ampoule: sérum calmante e hidratante de noni · 50 ml</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>254.9</v>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>The Real Noni Energy Ampoule Mist 50ml</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>50ml</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="I40" s="4" t="n"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-the-real-noni-energy-ampoule-mist-50ml</t>
+        </is>
+      </c>
+      <c r="L40" s="2">
+        <f>ROUND(H40*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M40" s="6">
+        <f>IF(OR(D40="",L40=""),"",D40/L40-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>CX0032</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Oil Control Mattifying Sun Stick: protetor solar em bastão matte FPS 50+ PA++++ 19 g</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>137.9</v>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Oil Control Mattifying Sun Stick 19g</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>19g</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="I41" s="4" t="n"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-oil-control-mattifying-sun-stick-19g</t>
+        </is>
+      </c>
+      <c r="L41" s="2">
+        <f>ROUND(H41*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M41" s="6">
+        <f>IF(OR(D41="",L41=""),"",D41/L41-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>CX0015-1</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Kit Noni Energy Ampoule + Heartleaf BHA Peeling Pad: sérum de noni e discos com BHA · Ampola 30 ml + discos</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>316.9</v>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>Conferir (tamanho/kit diferente)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ji Woo Gae Heartleaf BHA Peeling Pad 60Pads</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>60pad</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="I42" s="4" t="n"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-ji-woo-gae-heartleaf-bha-peeling-pad-60pads</t>
+        </is>
+      </c>
+      <c r="L42" s="2">
+        <f>ROUND(H42*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M42" s="6">
+        <f>IF(OR(D42="",L42=""),"",D42/L42-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>CX0015-2</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Kit Noni Energy Ampoule + Heartleaf BHA Peeling Pad: sérum de noni e discos com BHA · Ampola 50 ml + discos</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>367.9</v>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>Conferir (tamanho/kit diferente)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Ji Woo Gae Heartleaf BHA Peeling Pad 60Pads</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>60pad</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="I43" s="4" t="n"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-ji-woo-gae-heartleaf-bha-peeling-pad-60pads</t>
+        </is>
+      </c>
+      <c r="L43" s="2">
+        <f>ROUND(H43*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M43" s="6">
+        <f>IF(OR(D43="",L43=""),"",D43/L43-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>CX0028</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Kit The Real Cica Soothing &amp; Calming Duo: sérum e gel-creme calmantes de centella</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>335.9</v>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>Conferir (tamanho/kit diferente)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>The Real Cica Soothing Cream 50ml</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>50ml</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="I44" s="4" t="n"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-the-real-cica-soothing-cream-50ml</t>
+        </is>
+      </c>
+      <c r="L44" s="2">
+        <f>ROUND(H44*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M44" s="6">
+        <f>IF(OR(D44="",L44=""),"",D44/L44-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CX0031-2</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Pore+Dark Spot Brightening Cream Mask: máscara de creme com niacinamida 20 g · Caixa com 4</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>174.9</v>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>Conferir (tamanho/kit diferente)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Pore+Dark Spot Brightening Cream Mask - 2 Size</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1ea</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I45" s="4" t="n"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-pore-dark-spot-brightening-cream-mask-2-size?variant=67601354228021</t>
+        </is>
+      </c>
+      <c r="L45" s="2">
+        <f>ROUND(H45*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M45" s="6">
+        <f>IF(OR(D45="",L45=""),"",D45/L45-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CX0043-2</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Pore+Dark Spot Brightening Serum Mask: máscara em folha com niacinamida · Caixa com 10</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>210.9</v>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>Conferir (tamanho/kit diferente)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Pore+Dark Spot Brightening Serum Mask - 2 Size</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1ea</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I46" s="4" t="n"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-pore-dark-spot-brightening-serum-mask-2-size?variant=67601349935413</t>
+        </is>
+      </c>
+      <c r="L46" s="2">
+        <f>ROUND(H46*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M46" s="6">
+        <f>IF(OR(D46="",L46=""),"",D46/L46-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>CX0017-1</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>TXA Body Clarifying Pad: discos esfoliantes para o corpo com ácido tranexâmico 50 un. · 1 pote (50 discos)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>181.9</v>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>Conferir (tamanho/kit diferente)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Ji Woo Gae One Step Body Brightening Pad 60pads</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>60pad</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="I47" s="4" t="n"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-ji-woo-gae-one-step-body-brightening-pad-60pads</t>
+        </is>
+      </c>
+      <c r="L47" s="2">
+        <f>ROUND(H47*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M47" s="6">
+        <f>IF(OR(D47="",L47=""),"",D47/L47-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>CX0017-2</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>TXA Body Clarifying Pad: discos esfoliantes para o corpo com ácido tranexâmico 50 un. · 2 potes (100 discos)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>364.9</v>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>Conferir (tamanho/kit diferente)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Ji Woo Gae One Step Body Brightening Pad 60pads</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>60pad</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="I48" s="4" t="n"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-ji-woo-gae-one-step-body-brightening-pad-60pads</t>
+        </is>
+      </c>
+      <c r="L48" s="2">
+        <f>ROUND(H48*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M48" s="6">
+        <f>IF(OR(D48="",L48=""),"",D48/L48-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>CX0038-2</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>The Real Cica Calming Ampoule Mask: máscara em folha calmante de centella · Caixa com 5</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>Conferir (tamanho/kit diferente)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>The Real Cica Calming Serum Mask - 2 Size</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>10ea</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="I49" s="4" t="n"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-the-real-cica-calming-serum-mask-2-size?variant=67601249829173</t>
+        </is>
+      </c>
+      <c r="L49" s="2">
+        <f>ROUND(H49*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M49" s="6">
+        <f>IF(OR(D49="",L49=""),"",D49/L49-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>CX0039-2</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>The Real Cica Calming Serum Mask: máscara em folha de centella com sérum · Caixa com 10</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>210.9</v>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>Conferir (tamanho/kit diferente)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>The Real Cica Calming Serum Mask - 2 Size</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>10ea</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="I50" s="4" t="n"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-the-real-cica-calming-serum-mask-2-size?variant=67601249829173</t>
+        </is>
+      </c>
+      <c r="L50" s="2">
+        <f>ROUND(H50*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M50" s="6">
+        <f>IF(OR(D50="",L50=""),"",D50/L50-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>CX0042-2</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>The Real Noni Energy Ampoule Mask: máscara em folha com ampola de noni · Caixa com 10</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>210.9</v>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>Conferir (tamanho/kit diferente)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>The Real Noni Energy Ampoule Mask - 2 Size</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1ea</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I51" s="4" t="n"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-the-real-noni-energy-ampoule-mask-2-size?variant=67601377362229</t>
+        </is>
+      </c>
+      <c r="L51" s="2">
+        <f>ROUND(H51*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M51" s="6">
+        <f>IF(OR(D51="",L51=""),"",D51/L51-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>CX0013</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>The Real Noni Ultimate Eye Cream: creme para a área dos olhos com bakuchiol 25 ml</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>189.9</v>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>Conferir (tamanho/kit diferente)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>The Real Noni Ultimate Eye Cream 20ml</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>20ml</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="I52" s="4" t="n"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-the-real-noni-ultimate-eye-cream-20ml</t>
+        </is>
+      </c>
+      <c r="L52" s="2">
+        <f>ROUND(H52*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M52" s="6">
+        <f>IF(OR(D52="",L52=""),"",D52/L52-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>CX0040-2</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Ji Woo Gae Cica PHA Peel 2-Step Gel Mask: máscara em 2 passos com PHA e centella · Caixa com 4</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>Conferir (tamanho/kit diferente)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Ji Woo Gae Cica PHA Peel 2-Step Gel Mask - 2 Size</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1ea</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I53" s="4" t="n"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>https://www.celimax.com/products/celimax-ji-woo-gae-cica-pha-peel-2-step-gel-mask-2-size?variant=67601351180597</t>
+        </is>
+      </c>
+      <c r="L53" s="2">
+        <f>ROUND(H53*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M53" s="6">
+        <f>IF(OR(D53="",L53=""),"",D53/L53-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>CX0033</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Pore+Dark Spot Brightening Care Sunscreen: protetor solar FPS 50+ PA++++ 50 ml</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="n"/>
+      <c r="I54" s="4" t="n"/>
+      <c r="L54" s="2" t="n"/>
+      <c r="M54" s="6" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>CX0026</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>TXA Brightening Eye Patch: patches de hidrogel para os olhos 60 unidades</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="n"/>
+      <c r="I55" s="4" t="n"/>
+      <c r="L55" s="2" t="n"/>
+      <c r="M55" s="6" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -853,10 +3596,57 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId52"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId53"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2923,7 +5713,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Site oficial: https://www.celimax.com · loja "CELIMAX NEW" · moeda USD · lido em 30/10/2026 06:04 UTC</t>
+          <t>Site oficial: https://www.celimax.com · loja "CELIMAX NEW" · moeda USD · lido em 30/10/2026 06:05 UTC</t>
         </is>
       </c>
     </row>

--- a/tools/precos/planilhas/precos-oficiais-celimax.xlsx
+++ b/tools/precos/planilhas/precos-oficiais-celimax.xlsx
@@ -5713,7 +5713,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Site oficial: https://www.celimax.com · loja "CELIMAX NEW" · moeda USD · lido em 30/10/2026 06:05 UTC</t>
+          <t>Site oficial: https://www.celimax.com · loja "CELIMAX NEW" · moeda USD · lido em 30/10/2026 06:07 UTC</t>
         </is>
       </c>
     </row>
